--- a/data/trans_orig/IP74A3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
